--- a/worklog/v2.2.3/s10/v4/pjm/test/ods_budget_v2.xlsx
+++ b/worklog/v2.2.3/s10/v4/pjm/test/ods_budget_v2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>payable_amount</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>snapshot_date</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +504,11 @@
           <t>6.60</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,6 +551,11 @@
           <t>22.08</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -583,6 +598,11 @@
           <t>38.64</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +645,11 @@
           <t>60.07</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +692,11 @@
           <t>13.08</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -709,6 +739,11 @@
           <t>1.95</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -751,6 +786,11 @@
           <t>10.78</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -793,6 +833,11 @@
           <t>24.01</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -835,6 +880,11 @@
           <t>59.92</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -877,6 +927,11 @@
           <t>85.72</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -919,6 +974,11 @@
           <t>11.52</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -961,6 +1021,11 @@
           <t>2.90</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1003,6 +1068,11 @@
           <t>11.55</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1045,6 +1115,11 @@
           <t>34.50</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1087,6 +1162,11 @@
           <t>81.20</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1129,6 +1209,11 @@
           <t>76.95</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1171,6 +1256,11 @@
           <t>16.08</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1213,6 +1303,11 @@
           <t>3.07</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1255,6 +1350,11 @@
           <t>15.73</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1297,6 +1397,11 @@
           <t>44.99</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1339,6 +1444,11 @@
           <t>73.92</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1381,6 +1491,11 @@
           <t>102.60</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1423,6 +1538,11 @@
           <t>16.92</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1465,6 +1585,11 @@
           <t>4.03</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1505,6 +1630,11 @@
       <c r="H26" t="inlineStr">
         <is>
           <t>19.91</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
         </is>
       </c>
     </row>
